--- a/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628159739</v>
+        <v>10.84497671057569</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907176553339</v>
+        <v>37.78907326029844</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.685881792370026</v>
+        <v>4.643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>9.85576520293373</v>
+        <v>4.556291095409447</v>
       </c>
       <c r="D2" t="n">
-        <v>21.622993186036</v>
+        <v>24.74200564242812</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.99267010218054</v>
+        <v>16.44918278465531</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52896639060656</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D3" t="n">
-        <v>59.69026041820607</v>
+        <v>84.94572010995527</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.88578277560466</v>
+        <v>29.17557827480671</v>
       </c>
       <c r="C4" t="n">
-        <v>67.5786032218292</v>
+        <v>75.87437132271475</v>
       </c>
       <c r="D4" t="n">
-        <v>74.73848922890117</v>
+        <v>113.103226015458</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>36.00559705325178</v>
       </c>
       <c r="C5" t="n">
-        <v>97.63480918734531</v>
+        <v>116.8034331127643</v>
       </c>
       <c r="D5" t="n">
-        <v>56.52412407201012</v>
+        <v>83.12948685709868</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>33.93214590188251</v>
       </c>
       <c r="C6" t="n">
-        <v>133.2732325992088</v>
+        <v>114.4757093059951</v>
       </c>
       <c r="D6" t="n">
-        <v>42.38499363544755</v>
+        <v>52.20639766873265</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="C7" t="n">
-        <v>147.5007203291535</v>
+        <v>96.65698847391548</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>113.8238288303752</v>
+        <v>66.42504966933919</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>60.79374483777947</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -954,7 +954,7 @@
         <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.66728091694591</v>
+        <v>7.683011262438804</v>
       </c>
       <c r="C21" t="n">
-        <v>93.92419123258739</v>
+        <v>94.11688796487533</v>
       </c>
       <c r="D21" t="n">
-        <v>7.66728091694591</v>
+        <v>8.643387670243653</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.69708192774424</v>
+        <v>5.049128442941345</v>
       </c>
       <c r="C2" t="n">
-        <v>13.73955912093411</v>
+        <v>14.39045784884975</v>
       </c>
       <c r="D2" t="n">
-        <v>20.73156627057989</v>
+        <v>35.25946879802419</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.72268948351267</v>
+        <v>16.06630117999905</v>
       </c>
       <c r="C3" t="n">
-        <v>31.32266050399448</v>
+        <v>22.01078352921349</v>
       </c>
       <c r="D3" t="n">
-        <v>62.26243940333271</v>
+        <v>84.50884238156544</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>29.85200244303276</v>
       </c>
       <c r="C4" t="n">
-        <v>63.72426173495622</v>
+        <v>71.40741926839175</v>
       </c>
       <c r="D4" t="n">
-        <v>85.58680136082843</v>
+        <v>127.2443199474291</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.31332605303754</v>
+        <v>39.39262663290327</v>
       </c>
       <c r="C5" t="n">
-        <v>110.4957041129785</v>
+        <v>126.6454538478386</v>
       </c>
       <c r="D5" t="n">
-        <v>67.64241682260524</v>
+        <v>100.4327901444487</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>40.69442408873454</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5311134502562</v>
+        <v>148.1260936167588</v>
       </c>
       <c r="D6" t="n">
-        <v>49.50953672516665</v>
+        <v>64.40264939859078</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.13536767666159</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C7" t="n">
-        <v>169.7785392339221</v>
+        <v>128.0974587024196</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.19455027635689</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="C8" t="n">
-        <v>151.2922299629547</v>
+        <v>95.79894098040376</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>97.40311672914301</v>
+        <v>58.79687000734145</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>38.00836236991527</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>27.57729301229291</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.845061635137256</v>
+        <v>7.862606668461342</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9858012567843</v>
+        <v>102.2138866899975</v>
       </c>
       <c r="D21" t="n">
-        <v>8.825694339529413</v>
+        <v>9.828258335576677</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.322455215349459</v>
+        <v>6.348962403364123</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55775586919921</v>
+        <v>8.068002633500289</v>
       </c>
       <c r="D2" t="n">
-        <v>28.81920385816512</v>
+        <v>32.85124167950676</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.96460032938488</v>
+        <v>16.1595672119025</v>
       </c>
       <c r="C3" t="n">
-        <v>41.26776474801468</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="D3" t="n">
-        <v>63.24418710757953</v>
+        <v>90.11462177281473</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.76266340194631</v>
+        <v>29.80095156241193</v>
       </c>
       <c r="C4" t="n">
-        <v>69.42919764433444</v>
+        <v>63.09888844735099</v>
       </c>
       <c r="D4" t="n">
-        <v>93.14233169271189</v>
+        <v>135.4635117273834</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.27053006467818</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C5" t="n">
-        <v>113.2691413774758</v>
+        <v>127.283589855599</v>
       </c>
       <c r="D5" t="n">
-        <v>79.54610773659782</v>
+        <v>118.1533362061037</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="C6" t="n">
-        <v>155.4518949858485</v>
+        <v>171.3512990561256</v>
       </c>
       <c r="D6" t="n">
-        <v>56.63407981488576</v>
+        <v>76.3976428490783</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.9206269713388</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>184.9897381635222</v>
+        <v>163.8497648479756</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>51.08327829507428</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.12078032981814</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="C8" t="n">
-        <v>184.5882033524853</v>
+        <v>128.1769802664635</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="C9" t="n">
-        <v>135.0109260357256</v>
+        <v>83.6468678972367</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>77.44025891098842</v>
+        <v>51.10487674456772</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>44.42408361716816</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.00737693536383</v>
+        <v>8.025761797579611</v>
       </c>
       <c r="C21" t="n">
-        <v>110.1014328612527</v>
+        <v>110.3542247167196</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00922116920479</v>
+        <v>11.03542247167196</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.815873399958105</v>
+        <v>5.801147184394402</v>
       </c>
       <c r="C2" t="n">
-        <v>10.70301347169872</v>
+        <v>5.486006171331176</v>
       </c>
       <c r="D2" t="n">
-        <v>23.66208316775662</v>
+        <v>27.14532402242431</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.44489594093983</v>
+        <v>19.94911335029519</v>
       </c>
       <c r="C3" t="n">
-        <v>59.35155746024092</v>
+        <v>50.87907477259095</v>
       </c>
       <c r="D3" t="n">
-        <v>68.68306938910686</v>
+        <v>98.18949664024474</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.7904711328347</v>
+        <v>19.82050440103886</v>
       </c>
       <c r="C4" t="n">
-        <v>94.53346818962962</v>
+        <v>98.05597895246717</v>
       </c>
       <c r="D4" t="n">
-        <v>89.39009196708058</v>
+        <v>130.8944579118187</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.95526587842793</v>
+        <v>25.72178985126644</v>
       </c>
       <c r="C5" t="n">
-        <v>92.87333282174828</v>
+        <v>102.3717418603362</v>
       </c>
       <c r="D5" t="n">
-        <v>55.2233083638831</v>
+        <v>77.41080647986101</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.00256969468102</v>
+        <v>24.03023855684918</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8417623309589</v>
+        <v>107.9146893985137</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82647700272235</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>129.7742837812731</v>
+        <v>90.12934798837841</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>99.47067739428682</v>
+        <v>61.58503348740241</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70353755551324</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>59.12968247908112</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1971,7 +1971,7 @@
         <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526437753654543</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C2" t="n">
-        <v>5.213080309550564</v>
+        <v>2.756747553525043</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47765346807846</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.79832511446868</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="C3" t="n">
-        <v>51.45830591809656</v>
+        <v>36.58973693727862</v>
       </c>
       <c r="D3" t="n">
-        <v>72.13391256953439</v>
+        <v>98.57728698342224</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.67783218875358</v>
+        <v>27.68234001664731</v>
       </c>
       <c r="C4" t="n">
-        <v>123.7345719047467</v>
+        <v>114.6092269937726</v>
       </c>
       <c r="D4" t="n">
-        <v>100.3660313005599</v>
+        <v>146.0820948965169</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.97414006898687</v>
+        <v>28.78975142703772</v>
       </c>
       <c r="C5" t="n">
-        <v>131.2351243651924</v>
+        <v>140.7335334037803</v>
       </c>
       <c r="D5" t="n">
-        <v>69.1641257641878</v>
+        <v>98.29748888771192</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3046895834737</v>
+        <v>135.2053120811665</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>43.1095234411817</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>154.7470001341992</v>
+        <v>115.7608170508541</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>126.341112059522</v>
+        <v>81.69613520889833</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>64.89843198923538</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>35.73070769606267</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
         <v>21.04572553593887</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2268,7 +2268,7 @@
         <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.157300616857742</v>
+        <v>3.387029579651496</v>
       </c>
       <c r="C2" t="n">
-        <v>12.13145638137784</v>
+        <v>8.998699457126264</v>
       </c>
       <c r="D2" t="n">
-        <v>15.41638419978766</v>
+        <v>21.60728522276805</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3755517068368</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="C3" t="n">
-        <v>34.83731728519807</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="D3" t="n">
-        <v>68.67816065058562</v>
+        <v>91.3516238801657</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.03817465394117</v>
+        <v>33.00439432136928</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2698453877395</v>
+        <v>102.6888463688079</v>
       </c>
       <c r="D4" t="n">
-        <v>111.5334114363674</v>
+        <v>159.6233409811931</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>34.70478134512475</v>
       </c>
       <c r="C5" t="n">
-        <v>177.6717907760665</v>
+        <v>176.6164119940012</v>
       </c>
       <c r="D5" t="n">
-        <v>86.07472996983911</v>
+        <v>123.3565990386117</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>172.2770871412303</v>
+        <v>176.1009944492716</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>59.53219903782235</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>22.81679839440012</v>
       </c>
       <c r="C7" t="n">
-        <v>176.126519889582</v>
+        <v>153.6690411549362</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>163.3922704177967</v>
+        <v>114.407968714402</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>104.5031161262559</v>
+        <v>68.22655670663207</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2579,7 +2579,7 @@
         <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.898700060013331</v>
+        <v>1.994911335029519</v>
       </c>
       <c r="C2" t="n">
-        <v>5.768749510154257</v>
+        <v>4.198934931063608</v>
       </c>
       <c r="D2" t="n">
-        <v>10.74915561379833</v>
+        <v>15.09927969131594</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67360209830033</v>
+        <v>15.88467785471339</v>
       </c>
       <c r="C3" t="n">
-        <v>42.29859983747383</v>
+        <v>29.65368940677491</v>
       </c>
       <c r="D3" t="n">
-        <v>68.01057221169779</v>
+        <v>91.03746461480672</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.3820073346058</v>
+        <v>36.09297259892973</v>
       </c>
       <c r="C4" t="n">
-        <v>125.2150474427509</v>
+        <v>96.35853717182444</v>
       </c>
       <c r="D4" t="n">
-        <v>119.7143150558561</v>
+        <v>169.7697035045839</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.09181092477625</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C5" t="n">
-        <v>217.5307475684871</v>
+        <v>209.0877173119645</v>
       </c>
       <c r="D5" t="n">
-        <v>91.0325558762855</v>
+        <v>129.9833960422777</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.54471541160352</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>210.9589284362589</v>
+        <v>209.5098688247906</v>
       </c>
       <c r="D6" t="n">
-        <v>46.28940425523712</v>
+        <v>57.80137783523521</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>7.60559946480004</v>
       </c>
       <c r="C7" t="n">
-        <v>194.9309154167254</v>
+        <v>156.3639386030937</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>126.6749062789659</v>
+        <v>85.03407740333748</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2876,7 +2876,7 @@
         <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.957024085191393</v>
+        <v>2.64384656753666</v>
       </c>
       <c r="C2" t="n">
-        <v>9.619164006210248</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12797135891735</v>
+        <v>14.72130682518092</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.18210635137117</v>
+        <v>11.52571804785755</v>
       </c>
       <c r="C3" t="n">
-        <v>32.41730919422968</v>
+        <v>22.91399141712056</v>
       </c>
       <c r="D3" t="n">
-        <v>62.14953841734433</v>
+        <v>83.67926557147689</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2423781764245</v>
+        <v>33.70634392990574</v>
       </c>
       <c r="C4" t="n">
-        <v>115.5791937255685</v>
+        <v>86.21217464843366</v>
       </c>
       <c r="D4" t="n">
-        <v>124.8449285582499</v>
+        <v>174.8875542868226</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.70035563268903</v>
+        <v>43.78594760940775</v>
       </c>
       <c r="C5" t="n">
-        <v>225.3601855098554</v>
+        <v>196.2268223863313</v>
       </c>
       <c r="D5" t="n">
-        <v>108.2867717784232</v>
+        <v>154.3061954149925</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>35.74347041621788</v>
       </c>
       <c r="C6" t="n">
-        <v>271.2961605915636</v>
+        <v>264.7351406840822</v>
       </c>
       <c r="D6" t="n">
-        <v>59.49194738194822</v>
+        <v>77.92720577229484</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>245.2955543922911</v>
+        <v>220.2030648194468</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>180.1654299448534</v>
+        <v>133.5176877775662</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>80.98436812331937</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.978221624057323</v>
+        <v>1.718058482431918</v>
       </c>
       <c r="C2" t="n">
-        <v>4.727115195948392</v>
+        <v>2.843141351498763</v>
       </c>
       <c r="D2" t="n">
-        <v>14.31584502332699</v>
+        <v>11.48841163509617</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.78449853115121</v>
+        <v>10.57342277473815</v>
       </c>
       <c r="C3" t="n">
-        <v>34.90603962449534</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>62.05627238544088</v>
+        <v>78.7214396650305</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.22212132753381</v>
+        <v>30.0562059655161</v>
       </c>
       <c r="C4" t="n">
-        <v>104.1820846269673</v>
+        <v>76.15515116612933</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8231501823072</v>
+        <v>176.5722333473101</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.94012305670351</v>
+        <v>47.73748211900116</v>
       </c>
       <c r="C5" t="n">
-        <v>226.0719525954343</v>
+        <v>188.8637146044802</v>
       </c>
       <c r="D5" t="n">
-        <v>120.9758608558132</v>
+        <v>170.3086829942154</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>41.74096714146165</v>
       </c>
       <c r="C6" t="n">
-        <v>312.0308363361723</v>
+        <v>292.9112997959657</v>
       </c>
       <c r="D6" t="n">
-        <v>68.99133816824036</v>
+        <v>94.3901330248096</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>14.31289978021425</v>
       </c>
       <c r="C7" t="n">
-        <v>299.2533899653999</v>
+        <v>276.0173853012865</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>47.07087542781757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>223.3083328079795</v>
+        <v>172.8219571170873</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>89.97030486029041</v>
+        <v>65.67499442329461</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.828415135935061</v>
+        <v>2.639919576719673</v>
       </c>
       <c r="C2" t="n">
-        <v>11.9125266433308</v>
+        <v>11.69948739150924</v>
       </c>
       <c r="D2" t="n">
-        <v>14.97557948058085</v>
+        <v>16.35493500504761</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.821003122657592</v>
+        <v>8.325220532012953</v>
       </c>
       <c r="C3" t="n">
-        <v>27.22877257728529</v>
+        <v>16.67498475663207</v>
       </c>
       <c r="D3" t="n">
-        <v>59.82279635827939</v>
+        <v>71.12762117268142</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.8700337546077</v>
+        <v>25.34676222824415</v>
       </c>
       <c r="C4" t="n">
-        <v>96.46063893306611</v>
+        <v>66.23851760553229</v>
       </c>
       <c r="D4" t="n">
-        <v>126.3892176970301</v>
+        <v>175.2449104511684</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>46.68210333693584</v>
       </c>
       <c r="C5" t="n">
-        <v>211.2230185687013</v>
+        <v>167.8297700409923</v>
       </c>
       <c r="D5" t="n">
-        <v>133.8122120888403</v>
+        <v>187.8574232076272</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.16614601285853</v>
+        <v>50.19381487502668</v>
       </c>
       <c r="C6" t="n">
-        <v>331.4321344674977</v>
+        <v>296.8962137275034</v>
       </c>
       <c r="D6" t="n">
-        <v>84.24671574453156</v>
+        <v>116.2467821644563</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>25.930902112271</v>
       </c>
       <c r="C7" t="n">
-        <v>361.8348973726129</v>
+        <v>338.0599132188679</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>57.55103217065227</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>287.7306171606552</v>
+        <v>245.3387512912779</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>155.645299283585</v>
+        <v>119.2578023733813</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>57.65313393189394</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.012803777884214</v>
+        <v>4.326562132615694</v>
       </c>
       <c r="C2" t="n">
-        <v>15.62844170390497</v>
+        <v>5.478152189697202</v>
       </c>
       <c r="D2" t="n">
-        <v>5.367214699117312</v>
+        <v>8.755226026473055</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.065597169735289</v>
+        <v>1.907535789351553</v>
       </c>
       <c r="C2" t="n">
-        <v>6.957645979997145</v>
+        <v>6.738716241950107</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1408729477928</v>
+        <v>12.16778104643497</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83987731321653</v>
+        <v>11.30482481440202</v>
       </c>
       <c r="C3" t="n">
-        <v>37.00697971158352</v>
+        <v>27.50857067299563</v>
       </c>
       <c r="D3" t="n">
-        <v>65.35494467171017</v>
+        <v>77.39117152577607</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.02915899815369</v>
+        <v>35.36549755008285</v>
       </c>
       <c r="C4" t="n">
-        <v>133.6384427451886</v>
+        <v>95.38857044002859</v>
       </c>
       <c r="D4" t="n">
-        <v>128.3163884404666</v>
+        <v>179.8905405876643</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.82058651649687</v>
+        <v>29.13336312352411</v>
       </c>
       <c r="C5" t="n">
-        <v>296.2178260638689</v>
+        <v>251.6464802910637</v>
       </c>
       <c r="D5" t="n">
-        <v>122.0066959452724</v>
+        <v>169.9896149903352</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.62393387601124</v>
+        <v>16.1006623496477</v>
       </c>
       <c r="C6" t="n">
-        <v>296.7754587598811</v>
+        <v>277.9376838107933</v>
       </c>
       <c r="D6" t="n">
-        <v>68.26680836250623</v>
+        <v>89.92219922278237</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>202.3568550516483</v>
+        <v>172.5333232920387</v>
       </c>
       <c r="D7" t="n">
-        <v>31.62013005838127</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>114.658314378985</v>
+        <v>87.87132826861075</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.959208564778139</v>
+        <v>5.627377840742716</v>
       </c>
       <c r="C2" t="n">
-        <v>6.573782627636643</v>
+        <v>6.981207924899069</v>
       </c>
       <c r="D2" t="n">
-        <v>15.20432669567035</v>
+        <v>28.32931175374596</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.65196259107789</v>
+        <v>9.198975988792613</v>
       </c>
       <c r="C3" t="n">
-        <v>39.3828091558608</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="D3" t="n">
-        <v>7.642905877561418</v>
+        <v>10.48997421987717</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39753726423073</v>
+        <v>13.39881642396798</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14004803038441</v>
+        <v>70.14674480783238</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57618085461538</v>
+        <v>1.576331343996233</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.566108572451915</v>
+        <v>4.013384614960961</v>
       </c>
       <c r="C2" t="n">
-        <v>5.05403718146258</v>
+        <v>4.701589755637975</v>
       </c>
       <c r="D2" t="n">
-        <v>14.34235221134165</v>
+        <v>24.49951395947916</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.60135367881356</v>
+        <v>15.32017292477148</v>
       </c>
       <c r="C3" t="n">
-        <v>30.78269926665874</v>
+        <v>22.28076414788136</v>
       </c>
       <c r="D3" t="n">
-        <v>18.56484908730718</v>
+        <v>31.74972075534185</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.46917759163874</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="C4" t="n">
-        <v>60.54634441630929</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D4" t="n">
-        <v>19.08026663203676</v>
+        <v>20.57350489019616</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43747079771087</v>
+        <v>15.44093375869728</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12483708196594</v>
+        <v>86.144156759048</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249993852149658</v>
+        <v>3.250722896567849</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.499349728563132</v>
+        <v>4.040873550679871</v>
       </c>
       <c r="C2" t="n">
-        <v>3.389974822764236</v>
+        <v>4.998077562320511</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9137704329423</v>
+        <v>34.75583222574558</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1595672119025</v>
+        <v>14.52004854581033</v>
       </c>
       <c r="C3" t="n">
-        <v>24.13626730890783</v>
+        <v>19.86075605691298</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7316073283089</v>
+        <v>43.9822971502571</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.64932044760141</v>
+        <v>21.50518346152638</v>
       </c>
       <c r="C4" t="n">
-        <v>69.55682484588651</v>
+        <v>41.84895938892878</v>
       </c>
       <c r="D4" t="n">
-        <v>24.09601565303371</v>
+        <v>31.84298678724529</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.11829275059513</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C5" t="n">
-        <v>66.07162049581035</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>30.06602344255857</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72564200340172</v>
+        <v>16.73433039676487</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0264162207505</v>
+        <v>102.0794154202657</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181410500850431</v>
+        <v>5.020299119029461</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.072690387843269</v>
+        <v>4.640721397974672</v>
       </c>
       <c r="C2" t="n">
-        <v>8.08861933528947</v>
+        <v>9.219592690581797</v>
       </c>
       <c r="D2" t="n">
-        <v>22.0382724649324</v>
+        <v>28.42061429024092</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7128720064702</v>
+        <v>14.15189315671777</v>
       </c>
       <c r="C3" t="n">
-        <v>17.88253443285565</v>
+        <v>19.58095796120263</v>
       </c>
       <c r="D3" t="n">
-        <v>35.14165907351457</v>
+        <v>60.61310326019807</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.54195009494002</v>
+        <v>25.19360958638165</v>
       </c>
       <c r="C4" t="n">
-        <v>63.83912621635309</v>
+        <v>46.23933512232053</v>
       </c>
       <c r="D4" t="n">
-        <v>31.16656261901924</v>
+        <v>45.92026711844031</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.29196428325558</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>99.77011044408214</v>
+        <v>53.16163818496479</v>
       </c>
       <c r="D5" t="n">
-        <v>31.26866438026092</v>
+        <v>34.23845118560752</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.42517887139688</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>60.0554705641859</v>
+        <v>26.96860943565989</v>
       </c>
       <c r="D6" t="n">
         <v>38.07806645691679</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.042855665064</v>
+        <v>18.05897017929687</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7081536244651</v>
+        <v>117.8132816458891</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014285221687999</v>
+        <v>6.879607687351189</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.540002295064751</v>
+        <v>4.642684893383167</v>
       </c>
       <c r="C2" t="n">
-        <v>5.942518853805943</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D2" t="n">
-        <v>20.81108783462389</v>
+        <v>27.30927588903353</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.72621556370216</v>
+        <v>13.46957850226624</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92519155249477</v>
+        <v>27.14041528390307</v>
       </c>
       <c r="D3" t="n">
-        <v>41.46411428886404</v>
+        <v>64.66281254021617</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.95638649485241</v>
+        <v>19.10579207234717</v>
       </c>
       <c r="C4" t="n">
-        <v>44.52913062152258</v>
+        <v>39.97283952611313</v>
       </c>
       <c r="D4" t="n">
-        <v>35.93981995706723</v>
+        <v>56.65371476897069</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.68404147014855</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="C5" t="n">
-        <v>80.47876805563229</v>
+        <v>51.98354093986863</v>
       </c>
       <c r="D5" t="n">
-        <v>28.32342126752049</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>74.90833158173589</v>
+        <v>38.60133798328035</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>34.13536767666159</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048034690353932</v>
+        <v>7.057989720085803</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0753252220681</v>
+        <v>66.16865362580441</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405021681471207</v>
+        <v>5.293492290064353</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.322635141798706</v>
+        <v>4.897939296487337</v>
       </c>
       <c r="C2" t="n">
-        <v>9.149888603580273</v>
+        <v>7.003788122096745</v>
       </c>
       <c r="D2" t="n">
-        <v>24.09110691451248</v>
+        <v>36.00854229636451</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C3" t="n">
-        <v>23.46867887002</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D3" t="n">
-        <v>48.92539684113979</v>
+        <v>71.9768329368549</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.70411839258999</v>
+        <v>23.78971036930871</v>
       </c>
       <c r="C4" t="n">
-        <v>54.29261154025711</v>
+        <v>57.63644422092175</v>
       </c>
       <c r="D4" t="n">
-        <v>48.98331995569036</v>
+        <v>76.8571007746658</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.77716863333176</v>
+        <v>24.49460522095793</v>
       </c>
       <c r="C5" t="n">
-        <v>81.80412745636549</v>
+        <v>65.4580281806561</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>48.20381227851841</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.20633124880786</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="C6" t="n">
-        <v>106.3046231635489</v>
+        <v>64.16113946334606</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>77.25372684718151</v>
+        <v>40.96244121199391</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>34.13045893814036</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267815142295354</v>
+        <v>7.280050584496059</v>
       </c>
       <c r="C21" t="n">
-        <v>75.4035821013143</v>
+        <v>75.53052481414662</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450861356721515</v>
+        <v>6.370044261434051</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.657411108946868</v>
+        <v>4.917574250572273</v>
       </c>
       <c r="C2" t="n">
-        <v>5.082507864885738</v>
+        <v>6.178138302825178</v>
       </c>
       <c r="D2" t="n">
-        <v>20.7610187017073</v>
+        <v>26.05362057530185</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24301576676348</v>
+        <v>16.21847207415731</v>
       </c>
       <c r="C3" t="n">
-        <v>30.68943323475529</v>
+        <v>30.65016332658542</v>
       </c>
       <c r="D3" t="n">
-        <v>56.84319207589032</v>
+        <v>84.08178213021807</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.26040948799944</v>
+        <v>27.27393297168064</v>
       </c>
       <c r="C4" t="n">
-        <v>56.89620645191965</v>
+        <v>76.62737181187205</v>
       </c>
       <c r="D4" t="n">
-        <v>62.5118033202114</v>
+        <v>95.6948757237536</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.37942194439156</v>
+        <v>30.53235360207581</v>
       </c>
       <c r="C5" t="n">
-        <v>91.4497986505904</v>
+        <v>88.92179831215486</v>
       </c>
       <c r="D5" t="n">
-        <v>44.89041377668541</v>
+        <v>64.42719309119694</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.69943063824701</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>119.7889278813788</v>
+        <v>86.2190468823634</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>43.02902012943346</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>119.2342404284794</v>
+        <v>68.80971484295469</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>70.51402885752715</v>
+        <v>40.38910055271378</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474508928452122</v>
+        <v>7.488628053328325</v>
       </c>
       <c r="C21" t="n">
-        <v>85.02253906114288</v>
+        <v>85.1831441066097</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540195312395606</v>
+        <v>7.488628053328325</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497671057569</v>
+        <v>10.84497622422514</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907326029844</v>
+        <v>37.78907156562109</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.643666641087413</v>
+        <v>5.953318078552658</v>
       </c>
       <c r="C2" t="n">
-        <v>4.556291095409447</v>
+        <v>6.914449081010286</v>
       </c>
       <c r="D2" t="n">
-        <v>24.74200564242812</v>
+        <v>24.7312064176814</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44918278465531</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="C3" t="n">
-        <v>26.87534340375643</v>
+        <v>30.95450511490193</v>
       </c>
       <c r="D3" t="n">
-        <v>84.94572010995527</v>
+        <v>73.80779240527521</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.17557827480671</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>75.87437132271475</v>
+        <v>69.78655380868027</v>
       </c>
       <c r="D4" t="n">
-        <v>113.103226015458</v>
+        <v>82.06429059799088</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.00559705325178</v>
+        <v>48.76831720846032</v>
       </c>
       <c r="C5" t="n">
-        <v>116.8034331127643</v>
+        <v>122.2766765639403</v>
       </c>
       <c r="D5" t="n">
-        <v>83.12948685709868</v>
+        <v>54.51154127830416</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.93214590188251</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>114.4757093059951</v>
+        <v>135.688331951656</v>
       </c>
       <c r="D6" t="n">
-        <v>52.20639766873265</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>33.11729530735765</v>
       </c>
       <c r="C7" t="n">
-        <v>96.65698847391548</v>
+        <v>109.2331765653171</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C8" t="n">
-        <v>66.42504966933919</v>
+        <v>60.66709938393165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -954,7 +954,7 @@
         <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683011262438804</v>
+        <v>7.696251715716122</v>
       </c>
       <c r="C21" t="n">
-        <v>94.11688796487533</v>
+        <v>94.27908351752249</v>
       </c>
       <c r="D21" t="n">
-        <v>8.643387670243653</v>
+        <v>8.658283180180637</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.049128442941345</v>
+        <v>9.142034621946298</v>
       </c>
       <c r="C2" t="n">
-        <v>14.39045784884975</v>
+        <v>5.478152189697202</v>
       </c>
       <c r="D2" t="n">
-        <v>35.25946879802419</v>
+        <v>31.59656811347934</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.06630117999905</v>
+        <v>19.07535789351553</v>
       </c>
       <c r="C3" t="n">
-        <v>22.01078352921349</v>
+        <v>28.6866679180918</v>
       </c>
       <c r="D3" t="n">
-        <v>84.50884238156544</v>
+        <v>75.6240256581318</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.85200244303276</v>
+        <v>35.05919226635785</v>
       </c>
       <c r="C4" t="n">
-        <v>71.40741926839175</v>
+        <v>73.46221721338033</v>
       </c>
       <c r="D4" t="n">
-        <v>127.2443199474291</v>
+        <v>97.494419265638</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.39262663290327</v>
+        <v>51.39449231732053</v>
       </c>
       <c r="C5" t="n">
-        <v>126.6454538478386</v>
+        <v>124.0438224315845</v>
       </c>
       <c r="D5" t="n">
-        <v>100.4327901444487</v>
+        <v>68.18237805994099</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.69442408873454</v>
+        <v>55.78879504152925</v>
       </c>
       <c r="C6" t="n">
-        <v>148.1260936167588</v>
+        <v>163.5827294724206</v>
       </c>
       <c r="D6" t="n">
-        <v>64.40264939859078</v>
+        <v>47.33594730796422</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>44.19631814978291</v>
       </c>
       <c r="C7" t="n">
-        <v>128.0974587024196</v>
+        <v>148.9379989681709</v>
       </c>
       <c r="D7" t="n">
-        <v>45.03473068920969</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="C8" t="n">
-        <v>95.79894098040376</v>
+        <v>100.0548172783137</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>32.16303653882975</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.862606668461342</v>
+        <v>7.876204430776359</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2138866899975</v>
+        <v>102.3906576000927</v>
       </c>
       <c r="D21" t="n">
-        <v>9.828258335576677</v>
+        <v>9.845255538470449</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.348962403364123</v>
+        <v>9.950012982541423</v>
       </c>
       <c r="C2" t="n">
-        <v>8.068002633500289</v>
+        <v>6.705336820005715</v>
       </c>
       <c r="D2" t="n">
-        <v>32.85124167950676</v>
+        <v>32.43301715749762</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1595672119025</v>
+        <v>23.96937019918587</v>
       </c>
       <c r="C3" t="n">
-        <v>37.52239725631309</v>
+        <v>25.00511402716626</v>
       </c>
       <c r="D3" t="n">
-        <v>90.11462177281473</v>
+        <v>80.66530011943918</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.80095156241193</v>
+        <v>35.17405674775472</v>
       </c>
       <c r="C4" t="n">
-        <v>63.09888844735099</v>
+        <v>71.71372455211676</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4635117273834</v>
+        <v>107.8577480316673</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.25794727097221</v>
+        <v>51.54175447295756</v>
       </c>
       <c r="C5" t="n">
-        <v>127.283589855599</v>
+        <v>127.5290267816607</v>
       </c>
       <c r="D5" t="n">
-        <v>118.1533362061037</v>
+        <v>83.27674901273571</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>61.26302024040947</v>
       </c>
       <c r="C6" t="n">
-        <v>171.3512990561256</v>
+        <v>178.5563454575929</v>
       </c>
       <c r="D6" t="n">
-        <v>76.3976428490783</v>
+        <v>54.90325861229863</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>53.41885608347744</v>
       </c>
       <c r="C7" t="n">
-        <v>163.8497648479756</v>
+        <v>185.3490578232766</v>
       </c>
       <c r="D7" t="n">
-        <v>51.08327829507428</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>34.79804737702819</v>
       </c>
       <c r="C8" t="n">
-        <v>128.1769802664635</v>
+        <v>142.112888928247</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>17.74999849278232</v>
       </c>
       <c r="C9" t="n">
-        <v>83.6468678972367</v>
+        <v>82.20468051969816</v>
       </c>
       <c r="D9" t="n">
         <v>36.60937189136354</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.025761797579611</v>
+        <v>8.039727954518556</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3542247167196</v>
+        <v>110.5462593746302</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03542247167196</v>
+        <v>11.05462593746301</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.801147184394402</v>
+        <v>9.031097131366408</v>
       </c>
       <c r="C2" t="n">
-        <v>5.486006171331176</v>
+        <v>4.559236338522187</v>
       </c>
       <c r="D2" t="n">
-        <v>27.14532402242431</v>
+        <v>26.72022726648544</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94911335029519</v>
+        <v>26.63481521621597</v>
       </c>
       <c r="C3" t="n">
-        <v>50.87907477259095</v>
+        <v>39.4122615869882</v>
       </c>
       <c r="D3" t="n">
-        <v>98.18949664024474</v>
+        <v>86.31034941885834</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.82050440103886</v>
+        <v>24.75967710110456</v>
       </c>
       <c r="C4" t="n">
-        <v>98.05597895246717</v>
+        <v>102.8930498912912</v>
       </c>
       <c r="D4" t="n">
-        <v>130.8944579118187</v>
+        <v>100.3405058602495</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.72178985126644</v>
+        <v>34.50843180427539</v>
       </c>
       <c r="C5" t="n">
-        <v>102.3717418603362</v>
+        <v>106.6914317590221</v>
       </c>
       <c r="D5" t="n">
-        <v>77.41080647986101</v>
+        <v>55.17422097867075</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.03023855684918</v>
+        <v>33.16736444027425</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9146893985137</v>
+        <v>122.0832722662036</v>
       </c>
       <c r="D6" t="n">
-        <v>33.61013265488955</v>
+        <v>28.73968229412113</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>90.12934798837841</v>
+        <v>99.89086541170445</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58503348740241</v>
+        <v>60.58365082907067</v>
       </c>
       <c r="D8" t="n">
         <v>26.95388322009618</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.473423377625215</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C2" t="n">
-        <v>2.756747553525043</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="D2" t="n">
-        <v>18.8358114536793</v>
+        <v>18.58939277991335</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4988920646734</v>
+        <v>29.42297869627691</v>
       </c>
       <c r="C3" t="n">
-        <v>36.58973693727862</v>
+        <v>28.97137475232337</v>
       </c>
       <c r="D3" t="n">
-        <v>98.57728698342224</v>
+        <v>87.76824475966485</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.68234001664731</v>
+        <v>35.87600635629119</v>
       </c>
       <c r="C4" t="n">
-        <v>114.6092269937726</v>
+        <v>103.5184231788964</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0820948965169</v>
+        <v>118.2721276783175</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.78975142703772</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>140.7335334037803</v>
+        <v>147.2130682518092</v>
       </c>
       <c r="D5" t="n">
-        <v>98.29748888771192</v>
+        <v>71.74121348783568</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>39.00385454202154</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2053120811665</v>
+        <v>146.5965306935422</v>
       </c>
       <c r="D6" t="n">
-        <v>43.1095234411817</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>115.7608170508541</v>
+        <v>131.0917892003723</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>81.69613520889833</v>
+        <v>82.6140693123691</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.387029579651496</v>
+        <v>4.788965301315941</v>
       </c>
       <c r="C2" t="n">
-        <v>8.998699457126264</v>
+        <v>3.888702656521616</v>
       </c>
       <c r="D2" t="n">
-        <v>21.60728522276805</v>
+        <v>17.31017552127976</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13502351929633</v>
+        <v>23.85156047467626</v>
       </c>
       <c r="C3" t="n">
-        <v>22.94344384824796</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="D3" t="n">
-        <v>91.3516238801657</v>
+        <v>83.31601892090556</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.00439432136928</v>
+        <v>46.00960615952677</v>
       </c>
       <c r="C4" t="n">
-        <v>102.6888463688079</v>
+        <v>87.55226026473055</v>
       </c>
       <c r="D4" t="n">
-        <v>159.6233409811931</v>
+        <v>132.6046624126167</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.70478134512475</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>176.6164119940012</v>
+        <v>168.5415371265712</v>
       </c>
       <c r="D5" t="n">
-        <v>123.3565990386117</v>
+        <v>93.46238144429635</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>44.80009298789471</v>
       </c>
       <c r="C6" t="n">
-        <v>176.1009944492716</v>
+        <v>189.384040887731</v>
       </c>
       <c r="D6" t="n">
-        <v>59.53219903782235</v>
+        <v>46.53091419048183</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>31.85967649821749</v>
       </c>
       <c r="C7" t="n">
-        <v>153.6690411549362</v>
+        <v>169.8384258438812</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>114.407968714402</v>
+        <v>123.5873097491097</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>68.22655670663207</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.994911335029519</v>
+        <v>2.861794557879453</v>
       </c>
       <c r="C2" t="n">
-        <v>4.198934931063608</v>
+        <v>1.829977720716055</v>
       </c>
       <c r="D2" t="n">
-        <v>15.09927969131594</v>
+        <v>12.10396744565893</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.88467785471339</v>
+        <v>23.02689240310894</v>
       </c>
       <c r="C3" t="n">
-        <v>29.65368940677491</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="D3" t="n">
-        <v>91.03746461480672</v>
+        <v>81.78449250228054</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.09297259892973</v>
+        <v>50.94877885959247</v>
       </c>
       <c r="C4" t="n">
-        <v>96.35853717182444</v>
+        <v>81.22195106774711</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7697035045839</v>
+        <v>142.661685894921</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.22649028670731</v>
+        <v>47.61476365597031</v>
       </c>
       <c r="C5" t="n">
-        <v>209.0877173119645</v>
+        <v>193.306122966197</v>
       </c>
       <c r="D5" t="n">
-        <v>129.9833960422777</v>
+        <v>99.20560551414022</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>37.99756314516856</v>
       </c>
       <c r="C6" t="n">
-        <v>209.5098688247906</v>
+        <v>228.0256305268855</v>
       </c>
       <c r="D6" t="n">
-        <v>57.80137783523521</v>
+        <v>46.0478943199924</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.60559946480004</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>156.3639386030937</v>
+        <v>173.1321893916293</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>85.03407740333748</v>
+        <v>86.78649705541802</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.64384656753666</v>
+        <v>3.750276230222815</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>7.344454575470388</v>
       </c>
       <c r="D2" t="n">
-        <v>14.72130682518092</v>
+        <v>12.61840324268425</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.52571804785755</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91399141712056</v>
+        <v>12.48292205949819</v>
       </c>
       <c r="D3" t="n">
-        <v>83.67926557147689</v>
+        <v>73.39545836949155</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.70634392990574</v>
+        <v>47.66875977970388</v>
       </c>
       <c r="C4" t="n">
-        <v>86.21217464843366</v>
+        <v>64.06885517914685</v>
       </c>
       <c r="D4" t="n">
-        <v>174.8875542868226</v>
+        <v>149.7449955810617</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.78594760940775</v>
+        <v>59.96024103687396</v>
       </c>
       <c r="C5" t="n">
-        <v>196.2268223863313</v>
+        <v>174.3829359668397</v>
       </c>
       <c r="D5" t="n">
-        <v>154.3061954149925</v>
+        <v>124.0438224315845</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.74347041621788</v>
+        <v>48.70450360768427</v>
       </c>
       <c r="C6" t="n">
-        <v>264.7351406840822</v>
+        <v>265.7414320809352</v>
       </c>
       <c r="D6" t="n">
-        <v>77.92720577229484</v>
+        <v>61.102013616913</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>220.2030648194468</v>
+        <v>243.1995230437241</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>38.0279973240002</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>133.5176877775662</v>
+        <v>144.4494484643544</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.718058482431918</v>
+        <v>2.812707172667112</v>
       </c>
       <c r="C2" t="n">
-        <v>2.843141351498763</v>
+        <v>3.59810533606456</v>
       </c>
       <c r="D2" t="n">
-        <v>11.48841163509617</v>
+        <v>9.842020735074273</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.57342277473815</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>20.04728812071987</v>
       </c>
       <c r="D3" t="n">
-        <v>78.7214396650305</v>
+        <v>68.16274310585605</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.0562059655161</v>
+        <v>42.33394275482671</v>
       </c>
       <c r="C4" t="n">
-        <v>76.15515116612933</v>
+        <v>51.52310126657686</v>
       </c>
       <c r="D4" t="n">
-        <v>176.5722333473101</v>
+        <v>152.1443869702409</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.73748211900116</v>
+        <v>66.14525157362885</v>
       </c>
       <c r="C5" t="n">
-        <v>188.8637146044802</v>
+        <v>158.7731474693154</v>
       </c>
       <c r="D5" t="n">
-        <v>170.3086829942154</v>
+        <v>141.5189315671777</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>57.39886127649402</v>
       </c>
       <c r="C6" t="n">
-        <v>292.9112997959657</v>
+        <v>283.1703990744288</v>
       </c>
       <c r="D6" t="n">
-        <v>94.3901330248096</v>
+        <v>73.86178852900879</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.31289978021425</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>276.0173853012865</v>
+        <v>297.0375853969149</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>172.8219571170873</v>
+        <v>189.2613224247001</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>69.33593161243097</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.639919576719673</v>
+        <v>4.559236338522187</v>
       </c>
       <c r="C2" t="n">
-        <v>11.69948739150924</v>
+        <v>3.785619147575701</v>
       </c>
       <c r="D2" t="n">
-        <v>16.35493500504761</v>
+        <v>21.26956401250714</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.325220532012953</v>
+        <v>12.43874341280709</v>
       </c>
       <c r="C3" t="n">
-        <v>16.67498475663207</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="D3" t="n">
-        <v>71.12762117268142</v>
+        <v>61.52121988662638</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.34676222824415</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>66.23851760553229</v>
+        <v>50.70628717664351</v>
       </c>
       <c r="D4" t="n">
-        <v>175.2449104511684</v>
+        <v>151.1233693578243</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.68210333693584</v>
+        <v>65.75255249193013</v>
       </c>
       <c r="C5" t="n">
-        <v>167.8297700409923</v>
+        <v>130.8178815908875</v>
       </c>
       <c r="D5" t="n">
-        <v>187.8574232076272</v>
+        <v>157.4968754537946</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.19381487502668</v>
+        <v>68.70957657712154</v>
       </c>
       <c r="C6" t="n">
-        <v>296.8962137275034</v>
+        <v>271.7389288061789</v>
       </c>
       <c r="D6" t="n">
-        <v>116.2467821644563</v>
+        <v>91.93478201648833</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="C7" t="n">
-        <v>338.0599132188679</v>
+        <v>347.2824511525624</v>
       </c>
       <c r="D7" t="n">
-        <v>57.55103217065227</v>
+        <v>50.96350507515617</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>245.3387512912779</v>
+        <v>268.3705524329081</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>119.2578023733813</v>
+        <v>130.6843639031099</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>48.82722207071512</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.326562132615694</v>
+        <v>6.291039288813561</v>
       </c>
       <c r="C2" t="n">
-        <v>5.478152189697202</v>
+        <v>4.080143458849744</v>
       </c>
       <c r="D2" t="n">
-        <v>8.755226026473055</v>
+        <v>4.858669388317464</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.907535789351553</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="C2" t="n">
-        <v>6.738716241950107</v>
+        <v>2.150027472300514</v>
       </c>
       <c r="D2" t="n">
-        <v>12.16778104643497</v>
+        <v>15.65396714421539</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.30482481440202</v>
+        <v>16.95478285234242</v>
       </c>
       <c r="C3" t="n">
-        <v>27.50857067299563</v>
+        <v>18.96245690752714</v>
       </c>
       <c r="D3" t="n">
-        <v>77.39117152577607</v>
+        <v>69.76790060229958</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.36549755008285</v>
+        <v>49.91499852702059</v>
       </c>
       <c r="C4" t="n">
-        <v>95.38857044002859</v>
+        <v>74.25350586300326</v>
       </c>
       <c r="D4" t="n">
-        <v>179.8905405876643</v>
+        <v>154.5693037997306</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.13336312352411</v>
+        <v>40.5216364927871</v>
       </c>
       <c r="C5" t="n">
-        <v>251.6464802910637</v>
+        <v>215.2972715413256</v>
       </c>
       <c r="D5" t="n">
-        <v>169.9896149903352</v>
+        <v>140.8562518668111</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1006623496477</v>
+        <v>22.70193391300324</v>
       </c>
       <c r="C6" t="n">
-        <v>277.9376838107933</v>
+        <v>282.0031010540794</v>
       </c>
       <c r="D6" t="n">
-        <v>89.92219922278237</v>
+        <v>74.22405343187586</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>172.5333232920387</v>
+        <v>188.7027079809837</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>87.87132826861075</v>
+        <v>96.29963230956963</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.86766934857171</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.627377840742716</v>
+        <v>7.160867754776235</v>
       </c>
       <c r="C2" t="n">
-        <v>6.981207924899069</v>
+        <v>5.391758391723482</v>
       </c>
       <c r="D2" t="n">
-        <v>28.32931175374596</v>
+        <v>10.69712298547324</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.198975988792613</v>
+        <v>13.36158625479909</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01935721664445</v>
+        <v>10.44088683466483</v>
       </c>
       <c r="D3" t="n">
-        <v>10.48997421987717</v>
+        <v>7.412195167063418</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39881642396798</v>
+        <v>13.39938963850075</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14674480783238</v>
+        <v>70.14974575450394</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576331343996233</v>
+        <v>1.576398781000089</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.013384614960961</v>
+        <v>6.17421131200819</v>
       </c>
       <c r="C2" t="n">
-        <v>4.701589755637975</v>
+        <v>8.470519192241479</v>
       </c>
       <c r="D2" t="n">
-        <v>24.49951395947916</v>
+        <v>12.58207857762712</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32017292477148</v>
+        <v>20.18473279931442</v>
       </c>
       <c r="C3" t="n">
-        <v>22.28076414788136</v>
+        <v>17.17567608579795</v>
       </c>
       <c r="D3" t="n">
-        <v>31.74972075534185</v>
+        <v>14.60349710067131</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.82278669161684</v>
+        <v>15.51946770873358</v>
       </c>
       <c r="C4" t="n">
-        <v>21.91359050649305</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D4" t="n">
-        <v>20.57350489019616</v>
+        <v>18.95263943048468</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44093375869728</v>
+        <v>15.44548069307538</v>
       </c>
       <c r="C21" t="n">
-        <v>86.144156759048</v>
+        <v>86.16952386663107</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250722896567849</v>
+        <v>3.251680145910606</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.040873550679871</v>
+        <v>5.43593703841459</v>
       </c>
       <c r="C2" t="n">
-        <v>4.998077562320511</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="D2" t="n">
-        <v>34.75583222574558</v>
+        <v>17.58899186928585</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52004854581033</v>
+        <v>21.11739311834889</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86075605691298</v>
+        <v>26.74771620220435</v>
       </c>
       <c r="D3" t="n">
-        <v>43.9822971502571</v>
+        <v>21.27938148954962</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.50518346152638</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C4" t="n">
-        <v>41.84895938892878</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="D4" t="n">
-        <v>31.84298678724529</v>
+        <v>22.01569226773472</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.842020735074275</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>25.37817815478006</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>29.28062527916113</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73433039676487</v>
+        <v>16.74419381485454</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0794154202657</v>
+        <v>102.1395822706127</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020299119029461</v>
+        <v>5.023258144456363</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.640721397974672</v>
+        <v>5.943500601510189</v>
       </c>
       <c r="C2" t="n">
-        <v>9.219592690581797</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>28.42061429024092</v>
+        <v>24.28745645536184</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.15189315671777</v>
+        <v>19.75276380944582</v>
       </c>
       <c r="C3" t="n">
-        <v>19.58095796120263</v>
+        <v>35.15638528907828</v>
       </c>
       <c r="D3" t="n">
-        <v>60.61310326019807</v>
+        <v>29.91385254840031</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.19360958638165</v>
+        <v>35.22510762837556</v>
       </c>
       <c r="C4" t="n">
-        <v>46.23933512232053</v>
+        <v>51.8804574309227</v>
       </c>
       <c r="D4" t="n">
-        <v>45.92026711844031</v>
+        <v>27.2101193709046</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93576979306323</v>
+        <v>28.78975142703772</v>
       </c>
       <c r="C5" t="n">
-        <v>53.16163818496479</v>
+        <v>41.60155896745859</v>
       </c>
       <c r="D5" t="n">
-        <v>34.23845118560752</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.740900721536855</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>26.96860943565989</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="D6" t="n">
         <v>38.07806645691679</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05897017929687</v>
+        <v>18.07601611780186</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8132816458891</v>
+        <v>117.9244861018502</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879607687351189</v>
+        <v>6.886101378210233</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.642684893383167</v>
+        <v>6.038730128822131</v>
       </c>
       <c r="C2" t="n">
-        <v>10.41437964665016</v>
+        <v>9.918597056005526</v>
       </c>
       <c r="D2" t="n">
-        <v>27.30927588903353</v>
+        <v>34.76564970278805</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.46957850226624</v>
+        <v>17.98070920328033</v>
       </c>
       <c r="C3" t="n">
-        <v>27.14041528390307</v>
+        <v>25.02965771977243</v>
       </c>
       <c r="D3" t="n">
-        <v>64.66281254021617</v>
+        <v>39.24536447726624</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.10579207234717</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="C4" t="n">
-        <v>39.97283952611313</v>
+        <v>59.9592592891697</v>
       </c>
       <c r="D4" t="n">
-        <v>56.65371476897069</v>
+        <v>30.83473189498382</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.13778883595982</v>
+        <v>25.05911015089984</v>
       </c>
       <c r="C5" t="n">
-        <v>51.98354093986863</v>
+        <v>52.96528864411543</v>
       </c>
       <c r="D5" t="n">
-        <v>34.18936380039518</v>
+        <v>27.36621725587985</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.34467555964864</v>
+        <v>14.16858286768997</v>
       </c>
       <c r="C6" t="n">
-        <v>38.60133798328035</v>
+        <v>30.5510068084565</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>19.3433750167749</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057989720085803</v>
+        <v>7.066511368326235</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16865362580441</v>
+        <v>66.24854407805844</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293492290064353</v>
+        <v>5.299883526244676</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.897939296487337</v>
+        <v>5.453608497091031</v>
       </c>
       <c r="C2" t="n">
-        <v>7.003788122096745</v>
+        <v>5.537057051952011</v>
       </c>
       <c r="D2" t="n">
-        <v>36.00854229636451</v>
+        <v>28.67488694564084</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.23181563138926</v>
+        <v>19.99820073550753</v>
       </c>
       <c r="C3" t="n">
-        <v>35.88287859022092</v>
+        <v>34.03719290623692</v>
       </c>
       <c r="D3" t="n">
-        <v>71.9768329368549</v>
+        <v>59.97987599095887</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.78971036930871</v>
+        <v>32.40454647407447</v>
       </c>
       <c r="C4" t="n">
-        <v>57.63644422092175</v>
+        <v>61.84814187214056</v>
       </c>
       <c r="D4" t="n">
-        <v>76.8571007746658</v>
+        <v>44.92477494633405</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.49460522095793</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="C5" t="n">
-        <v>65.4580281806561</v>
+        <v>88.94634200476104</v>
       </c>
       <c r="D5" t="n">
-        <v>48.20381227851841</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.43525839034661</v>
+        <v>25.76105975943631</v>
       </c>
       <c r="C6" t="n">
-        <v>64.16113946334606</v>
+        <v>62.59132488425541</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>32.56358960216246</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>40.96244121199391</v>
+        <v>33.35684174719388</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11524969649115</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280050584496059</v>
+        <v>7.290229837014074</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53052481414662</v>
+        <v>75.63613455902102</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370044261434051</v>
+        <v>6.378951107387315</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.917574250572273</v>
+        <v>4.987278337573796</v>
       </c>
       <c r="C2" t="n">
-        <v>6.178138302825178</v>
+        <v>8.921141388490765</v>
       </c>
       <c r="D2" t="n">
-        <v>26.05362057530185</v>
+        <v>27.07071119690155</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.21847207415731</v>
+        <v>19.3747909433108</v>
       </c>
       <c r="C3" t="n">
-        <v>30.65016332658542</v>
+        <v>26.46300936797277</v>
       </c>
       <c r="D3" t="n">
-        <v>84.08178213021807</v>
+        <v>69.00213739298707</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.27393297168064</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C4" t="n">
-        <v>76.62737181187205</v>
+        <v>75.64464235992098</v>
       </c>
       <c r="D4" t="n">
-        <v>95.6948757237536</v>
+        <v>64.87290654892499</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>42.5096755938869</v>
       </c>
       <c r="C5" t="n">
-        <v>88.92179831215486</v>
+        <v>102.641722479004</v>
       </c>
       <c r="D5" t="n">
-        <v>64.42719309119694</v>
+        <v>41.38066573400307</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>36.87051678069322</v>
       </c>
       <c r="C6" t="n">
-        <v>86.2190468823634</v>
+        <v>106.6266364105418</v>
       </c>
       <c r="D6" t="n">
-        <v>43.02902012943346</v>
+        <v>36.02523200733671</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>68.80971484295469</v>
+        <v>64.91708519561608</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>40.38910055271378</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.95781021091316</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.488628053328325</v>
+        <v>7.500739285499245</v>
       </c>
       <c r="C21" t="n">
-        <v>85.1831441066097</v>
+        <v>85.32090937255391</v>
       </c>
       <c r="D21" t="n">
-        <v>7.488628053328325</v>
+        <v>7.500739285499245</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_30_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622422514</v>
+        <v>10.84497643879504</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907156562109</v>
+        <v>37.789072313285</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.953318078552658</v>
+        <v>1.109374905798896</v>
       </c>
       <c r="C2" t="n">
-        <v>6.914449081010286</v>
+        <v>1.840776945462769</v>
       </c>
       <c r="D2" t="n">
-        <v>24.7312064176814</v>
+        <v>13.41165538771568</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05434028109884</v>
+        <v>11.66807146497334</v>
       </c>
       <c r="C3" t="n">
-        <v>30.95450511490193</v>
+        <v>23.50794877818987</v>
       </c>
       <c r="D3" t="n">
-        <v>73.80779240527521</v>
+        <v>65.76727870749383</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C4" t="n">
-        <v>69.78655380868027</v>
+        <v>83.95317318096176</v>
       </c>
       <c r="D4" t="n">
-        <v>82.06429059799088</v>
+        <v>65.26855087373644</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.76831720846032</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2766765639403</v>
+        <v>98.4692947359551</v>
       </c>
       <c r="D5" t="n">
-        <v>54.51154127830416</v>
+        <v>41.99425804915732</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>135.688331951656</v>
+        <v>73.17751037914877</v>
       </c>
       <c r="D6" t="n">
-        <v>40.37241084174159</v>
+        <v>29.06169554111408</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.11729530735765</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>109.2331765653171</v>
+        <v>44.85507085933252</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.10695374650067</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>60.66709938393165</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.696251715716122</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27908351752249</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.658283180180637</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.142034621946298</v>
+        <v>2.00669230748048</v>
       </c>
       <c r="C2" t="n">
-        <v>5.478152189697202</v>
+        <v>4.457134577280519</v>
       </c>
       <c r="D2" t="n">
-        <v>31.59656811347934</v>
+        <v>17.58015613994763</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.07535789351553</v>
+        <v>7.397468951499717</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6866679180918</v>
+        <v>13.81809893727386</v>
       </c>
       <c r="D3" t="n">
-        <v>75.6240256581318</v>
+        <v>61.869740321634</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.05919226635785</v>
+        <v>24.40232093675872</v>
       </c>
       <c r="C4" t="n">
-        <v>73.46221721338033</v>
+        <v>70.29706261488862</v>
       </c>
       <c r="D4" t="n">
-        <v>97.494419265638</v>
+        <v>82.56203668404402</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.39449231732053</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0438224315845</v>
+        <v>129.6643280383975</v>
       </c>
       <c r="D5" t="n">
-        <v>68.18237805994099</v>
+        <v>55.14967728606459</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.78879504152925</v>
+        <v>27.85414586489051</v>
       </c>
       <c r="C6" t="n">
-        <v>163.5827294724206</v>
+        <v>118.0178550229176</v>
       </c>
       <c r="D6" t="n">
-        <v>47.33594730796422</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.19631814978291</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9379989681709</v>
+        <v>76.59497413763189</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>100.0548172783137</v>
+        <v>45.31256528951153</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.876204430776359</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3906576000927</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.845255538470449</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.950012982541423</v>
+        <v>1.056360529769568</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705336820005715</v>
+        <v>1.831941216124548</v>
       </c>
       <c r="D2" t="n">
-        <v>32.43301715749762</v>
+        <v>11.86147576270996</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.96937019918587</v>
+        <v>7.849072895453249</v>
       </c>
       <c r="C3" t="n">
-        <v>25.00511402716626</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="D3" t="n">
-        <v>80.66530011943918</v>
+        <v>63.5141677262474</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.17405674775472</v>
+        <v>26.32949168019521</v>
       </c>
       <c r="C4" t="n">
-        <v>71.71372455211676</v>
+        <v>62.39693883881453</v>
       </c>
       <c r="D4" t="n">
-        <v>107.8577480316673</v>
+        <v>93.02746721131501</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.54175447295756</v>
+        <v>34.72932503773092</v>
       </c>
       <c r="C5" t="n">
-        <v>127.5290267816607</v>
+        <v>147.1639808665969</v>
       </c>
       <c r="D5" t="n">
-        <v>83.27674901273571</v>
+        <v>63.96086293167971</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.26302024040947</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C6" t="n">
-        <v>178.5563454575929</v>
+        <v>153.2380539127719</v>
       </c>
       <c r="D6" t="n">
-        <v>54.90325861229863</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.41885608347744</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>185.3490578232766</v>
+        <v>75.57690176832796</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.79804737702819</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>142.112888928247</v>
+        <v>42.39186586937727</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>82.20468051969816</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.039727954518556</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5462593746302</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05462593746301</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.031097131366408</v>
+        <v>1.509927969131594</v>
       </c>
       <c r="C2" t="n">
-        <v>4.559236338522187</v>
+        <v>6.853580723346982</v>
       </c>
       <c r="D2" t="n">
-        <v>26.72022726648544</v>
+        <v>11.84282255632927</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.63481521621597</v>
+        <v>5.659775514982861</v>
       </c>
       <c r="C3" t="n">
-        <v>39.4122615869882</v>
+        <v>11.02993545721291</v>
       </c>
       <c r="D3" t="n">
-        <v>86.31034941885834</v>
+        <v>58.39926218712152</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.75967710110456</v>
+        <v>21.05848825609408</v>
       </c>
       <c r="C4" t="n">
-        <v>102.8930498912912</v>
+        <v>51.17850782238623</v>
       </c>
       <c r="D4" t="n">
-        <v>100.3405058602495</v>
+        <v>103.3397450967235</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.50843180427539</v>
+        <v>37.89546138392689</v>
       </c>
       <c r="C5" t="n">
-        <v>106.6914317590221</v>
+        <v>132.8304643845935</v>
       </c>
       <c r="D5" t="n">
-        <v>55.17422097867075</v>
+        <v>82.49135084933826</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.16736444027425</v>
+        <v>32.60384125803657</v>
       </c>
       <c r="C6" t="n">
-        <v>122.0832722662036</v>
+        <v>195.4217892688489</v>
       </c>
       <c r="D6" t="n">
-        <v>28.73968229412113</v>
+        <v>46.12839763174064</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>99.89086541170445</v>
+        <v>147.2012872793582</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>60.58365082907067</v>
+        <v>70.09678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.416302084329653</v>
+        <v>0.9248063374004954</v>
       </c>
       <c r="C2" t="n">
-        <v>2.32674205906494</v>
+        <v>3.921100330761761</v>
       </c>
       <c r="D2" t="n">
-        <v>18.58939277991335</v>
+        <v>8.955502558139404</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.42297869627691</v>
+        <v>5.571418221600648</v>
       </c>
       <c r="C3" t="n">
-        <v>28.97137475232337</v>
+        <v>19.82148614874311</v>
       </c>
       <c r="D3" t="n">
-        <v>87.76824475966485</v>
+        <v>55.61600744558181</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.87600635629119</v>
+        <v>17.37006213123882</v>
       </c>
       <c r="C4" t="n">
-        <v>103.5184231788964</v>
+        <v>40.77689089589127</v>
       </c>
       <c r="D4" t="n">
-        <v>118.2721276783175</v>
+        <v>108.636273961135</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>38.36179154344412</v>
       </c>
       <c r="C5" t="n">
-        <v>147.2130682518092</v>
+        <v>120.2886374628405</v>
       </c>
       <c r="D5" t="n">
-        <v>71.74121348783568</v>
+        <v>97.16847902782808</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.00385454202154</v>
+        <v>39.44662275663685</v>
       </c>
       <c r="C6" t="n">
-        <v>146.5965306935422</v>
+        <v>211.7639615537413</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>55.8692983532775</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>131.0917892003723</v>
+        <v>203.6743604707475</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>82.6140693123691</v>
+        <v>105.3120762345553</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>51.47499562906875</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.788965301315941</v>
+        <v>1.443169125242811</v>
       </c>
       <c r="C2" t="n">
-        <v>3.888702656521616</v>
+        <v>7.649778111491146</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31017552127976</v>
+        <v>11.75348351524281</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.85156047467626</v>
+        <v>4.329507375728434</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4666743168825</v>
+        <v>17.44565670446582</v>
       </c>
       <c r="D3" t="n">
-        <v>83.31601892090556</v>
+        <v>50.22621254926682</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.00960615952677</v>
+        <v>14.17938209243668</v>
       </c>
       <c r="C4" t="n">
-        <v>87.55226026473055</v>
+        <v>45.29489383083509</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6046624126167</v>
+        <v>111.5461741565226</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>33.69848994827177</v>
       </c>
       <c r="C5" t="n">
-        <v>168.5415371265712</v>
+        <v>97.68389657255766</v>
       </c>
       <c r="D5" t="n">
-        <v>93.46238144429635</v>
+        <v>112.434655828866</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>45.56487444950297</v>
       </c>
       <c r="C6" t="n">
-        <v>189.384040887731</v>
+        <v>205.0419350227634</v>
       </c>
       <c r="D6" t="n">
-        <v>46.53091419048183</v>
+        <v>71.00392096194632</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.85967649821749</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>169.8384258438812</v>
+        <v>254.6977521558627</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>123.5873097491097</v>
+        <v>179.7481871705485</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>85.75468021825461</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.8226478228966</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.861794557879453</v>
+        <v>0.9464047868939253</v>
       </c>
       <c r="C2" t="n">
-        <v>1.829977720716055</v>
+        <v>3.855323234577225</v>
       </c>
       <c r="D2" t="n">
-        <v>12.10396744565893</v>
+        <v>8.46168346290326</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.02689240310894</v>
+        <v>6.165375582669969</v>
       </c>
       <c r="C3" t="n">
-        <v>18.23105486786327</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="D3" t="n">
-        <v>81.78449250228054</v>
+        <v>54.07957228843554</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.94877885959247</v>
+        <v>23.06223532046182</v>
       </c>
       <c r="C4" t="n">
-        <v>81.22195106774711</v>
+        <v>63.94122797759476</v>
       </c>
       <c r="D4" t="n">
-        <v>142.661685894921</v>
+        <v>116.3960078155018</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.61476365597031</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="C5" t="n">
-        <v>193.306122966197</v>
+        <v>159.7548951735622</v>
       </c>
       <c r="D5" t="n">
-        <v>99.20560551414022</v>
+        <v>104.5561305022853</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.99756314516856</v>
+        <v>17.14720540237479</v>
       </c>
       <c r="C6" t="n">
-        <v>228.0256305268855</v>
+        <v>221.9878821457676</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0478943199924</v>
+        <v>61.82654342264714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>173.1321893916293</v>
+        <v>126.360747013607</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>86.78649705541802</v>
+        <v>63.17055602976101</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.750276230222815</v>
+        <v>0.4800746273766903</v>
       </c>
       <c r="C2" t="n">
-        <v>7.344454575470388</v>
+        <v>2.128429022807085</v>
       </c>
       <c r="D2" t="n">
-        <v>12.61840324268425</v>
+        <v>6.194828013797373</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66025854106837</v>
+        <v>4.707480241863456</v>
       </c>
       <c r="C3" t="n">
-        <v>12.48292205949819</v>
+        <v>19.33552103514093</v>
       </c>
       <c r="D3" t="n">
-        <v>73.39545836949155</v>
+        <v>48.33143948007048</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.66875977970388</v>
+        <v>16.33628179866692</v>
       </c>
       <c r="C4" t="n">
-        <v>64.06885517914685</v>
+        <v>61.14619226360409</v>
       </c>
       <c r="D4" t="n">
-        <v>149.7449955810617</v>
+        <v>113.5499212208903</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.96024103687396</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="C5" t="n">
-        <v>174.3829359668397</v>
+        <v>125.9582304548658</v>
       </c>
       <c r="D5" t="n">
-        <v>124.0438224315845</v>
+        <v>108.7531019379404</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.70450360768427</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>265.7414320809352</v>
+        <v>198.1186502124149</v>
       </c>
       <c r="D6" t="n">
-        <v>61.102013616913</v>
+        <v>65.97246397768143</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>243.1995230437241</v>
+        <v>159.4780423209646</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>144.4494484643544</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.812707172667112</v>
+        <v>0.7824529202847079</v>
       </c>
       <c r="C2" t="n">
-        <v>3.59810533606456</v>
+        <v>7.264933011426397</v>
       </c>
       <c r="D2" t="n">
-        <v>9.842020735074273</v>
+        <v>8.930958865533233</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18272824617692</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C3" t="n">
-        <v>20.04728812071987</v>
+        <v>12.61545799957151</v>
       </c>
       <c r="D3" t="n">
-        <v>68.16274310585605</v>
+        <v>42.07279786549706</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.33394275482671</v>
+        <v>12.48194031179395</v>
       </c>
       <c r="C4" t="n">
-        <v>51.52310126657686</v>
+        <v>53.60342465187585</v>
       </c>
       <c r="D4" t="n">
-        <v>152.1443869702409</v>
+        <v>112.4140391270768</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.14525157362885</v>
+        <v>25.81996462169112</v>
       </c>
       <c r="C5" t="n">
-        <v>158.7731474693154</v>
+        <v>119.8713946885356</v>
       </c>
       <c r="D5" t="n">
-        <v>141.5189315671777</v>
+        <v>125.4182692175301</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.39886127649402</v>
+        <v>26.40508625342222</v>
       </c>
       <c r="C6" t="n">
-        <v>283.1703990744288</v>
+        <v>200.2922396296173</v>
       </c>
       <c r="D6" t="n">
-        <v>73.86178852900879</v>
+        <v>84.44797402390215</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>297.0375853969149</v>
+        <v>231.222201051913</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>189.2613224247001</v>
+        <v>145.7011767872691</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>61.23749480009903</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.559236338522187</v>
+        <v>1.009236639965721</v>
       </c>
       <c r="C2" t="n">
-        <v>3.785619147575701</v>
+        <v>9.793915097566181</v>
       </c>
       <c r="D2" t="n">
-        <v>21.26956401250714</v>
+        <v>18.27130652373739</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.43874341280709</v>
+        <v>2.817615911188346</v>
       </c>
       <c r="C3" t="n">
-        <v>17.05786636128833</v>
+        <v>21.72116795646068</v>
       </c>
       <c r="D3" t="n">
-        <v>61.52121988662638</v>
+        <v>39.50061888037042</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>9.010480429577225</v>
       </c>
       <c r="C4" t="n">
-        <v>50.70628717664351</v>
+        <v>40.98109441837461</v>
       </c>
       <c r="D4" t="n">
-        <v>151.1233693578243</v>
+        <v>108.4448331588069</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.75255249193013</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="C5" t="n">
-        <v>130.8178815908875</v>
+        <v>108.6549271675158</v>
       </c>
       <c r="D5" t="n">
-        <v>157.4968754537946</v>
+        <v>137.2728727463103</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.70957657712154</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>271.7389288061789</v>
+        <v>196.2670740422054</v>
       </c>
       <c r="D6" t="n">
-        <v>91.93478201648833</v>
+        <v>102.2392059202628</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.59071868498287</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="C7" t="n">
-        <v>347.2824511525624</v>
+        <v>263.8005168696392</v>
       </c>
       <c r="D7" t="n">
-        <v>50.96350507515617</v>
+        <v>58.03012505032471</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>268.3705524329081</v>
+        <v>228.6490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>130.6843639031099</v>
+        <v>120.9218647320796</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.291039288813561</v>
+        <v>8.140651963614552</v>
       </c>
       <c r="C2" t="n">
-        <v>4.080143458849744</v>
+        <v>11.03484419573415</v>
       </c>
       <c r="D2" t="n">
-        <v>4.858669388317464</v>
+        <v>9.394343781937728</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.262347621212151</v>
+        <v>1.036725575684632</v>
       </c>
       <c r="C2" t="n">
-        <v>2.150027472300514</v>
+        <v>14.32075376184822</v>
       </c>
       <c r="D2" t="n">
-        <v>15.65396714421539</v>
+        <v>21.27741799414112</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95478285234242</v>
+        <v>3.087596529856219</v>
       </c>
       <c r="C3" t="n">
-        <v>18.96245690752714</v>
+        <v>30.01202731882499</v>
       </c>
       <c r="D3" t="n">
-        <v>69.76790060229958</v>
+        <v>43.89393985687489</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.91499852702059</v>
+        <v>7.223699607848031</v>
       </c>
       <c r="C4" t="n">
-        <v>74.25350586300326</v>
+        <v>47.17101369365075</v>
       </c>
       <c r="D4" t="n">
-        <v>154.5693037997306</v>
+        <v>104.2076100672777</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.5216364927871</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C5" t="n">
-        <v>215.2972715413256</v>
+        <v>92.33337158441253</v>
       </c>
       <c r="D5" t="n">
-        <v>140.8562518668111</v>
+        <v>142.7215725048801</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.70193391300324</v>
+        <v>31.396291581813</v>
       </c>
       <c r="C6" t="n">
-        <v>282.0031010540794</v>
+        <v>186.1639084178015</v>
       </c>
       <c r="D6" t="n">
-        <v>74.22405343187586</v>
+        <v>119.7084245696306</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>188.7027079809837</v>
+        <v>273.5021476830061</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>70.66619975168541</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C8" t="n">
-        <v>96.29963230956963</v>
+        <v>288.398205599543</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>196.1374833452447</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>91.39089378833559</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.6666888066416</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.160867754776235</v>
+        <v>7.62425267118073</v>
       </c>
       <c r="C2" t="n">
-        <v>5.391758391723482</v>
+        <v>6.746570223584081</v>
       </c>
       <c r="D2" t="n">
-        <v>10.69712298547324</v>
+        <v>11.48252114887069</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.36158625479909</v>
+        <v>13.42539985557513</v>
       </c>
       <c r="C3" t="n">
-        <v>10.44088683466483</v>
+        <v>21.78498155723672</v>
       </c>
       <c r="D3" t="n">
-        <v>7.412195167063418</v>
+        <v>9.444412914854317</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39938963850075</v>
+        <v>11.67747711640471</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14974575450394</v>
+        <v>59.94438253087749</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576398781000089</v>
+        <v>0.7784984744269804</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.17421131200819</v>
+        <v>3.974114706791088</v>
       </c>
       <c r="C2" t="n">
-        <v>8.470519192241479</v>
+        <v>3.032618658418397</v>
       </c>
       <c r="D2" t="n">
-        <v>12.58207857762712</v>
+        <v>10.37216449536755</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.18473279931442</v>
+        <v>21.72607669498191</v>
       </c>
       <c r="C3" t="n">
+        <v>24.85785187152924</v>
+      </c>
+      <c r="D3" t="n">
         <v>17.17567608579795</v>
-      </c>
-      <c r="D3" t="n">
-        <v>14.60349710067131</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.51946770873358</v>
+        <v>16.42562083975339</v>
       </c>
       <c r="C4" t="n">
-        <v>16.70640068316797</v>
+        <v>35.93981995706723</v>
       </c>
       <c r="D4" t="n">
-        <v>18.95263943048468</v>
+        <v>19.16960567312322</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44548069307538</v>
+        <v>13.62757580020949</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16952386663107</v>
+        <v>73.74923374231018</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251680145910606</v>
+        <v>1.603244211789352</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43593703841459</v>
+        <v>3.5549084370777</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57833151325938</v>
+        <v>5.359360717483338</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58899186928585</v>
+        <v>15.96321767105314</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.11739311834889</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="C3" t="n">
-        <v>26.74771620220435</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D3" t="n">
-        <v>21.27938148954962</v>
+        <v>21.73589417202438</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.77993394999525</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>32.02166486941822</v>
+        <v>52.26333903557895</v>
       </c>
       <c r="D4" t="n">
-        <v>22.01569226773472</v>
+        <v>23.71313404837746</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.71992416684918</v>
+        <v>14.62804079327748</v>
       </c>
       <c r="C5" t="n">
-        <v>20.15037162966578</v>
+        <v>41.8469958935203</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>26.8262560185441</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74419381485454</v>
+        <v>14.8374684835829</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1395822706127</v>
+        <v>87.37620329221041</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023258144456363</v>
+        <v>2.472911413930483</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.943500601510189</v>
+        <v>2.605558407071035</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>5.65388502875738</v>
       </c>
       <c r="D2" t="n">
-        <v>24.28745645536184</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.75276380944582</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="C3" t="n">
-        <v>35.15638528907828</v>
+        <v>19.17353266394021</v>
       </c>
       <c r="D3" t="n">
-        <v>29.91385254840031</v>
+        <v>29.46224860444678</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.22510762837556</v>
+        <v>32.80019079888594</v>
       </c>
       <c r="C4" t="n">
-        <v>51.8804574309227</v>
+        <v>45.99684343937156</v>
       </c>
       <c r="D4" t="n">
-        <v>27.2101193709046</v>
+        <v>29.27768003604838</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.78975142703772</v>
+        <v>32.47130531796326</v>
       </c>
       <c r="C5" t="n">
-        <v>41.60155896745859</v>
+        <v>72.64933011426398</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="C6" t="n">
-        <v>22.54092728950677</v>
+        <v>41.62021217383928</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07601611780186</v>
+        <v>16.07961877181417</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9244861018502</v>
+        <v>101.555486979879</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886101378210233</v>
+        <v>3.3851828993293</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.038730128822131</v>
+        <v>2.307107104980004</v>
       </c>
       <c r="C2" t="n">
-        <v>9.918597056005526</v>
+        <v>7.36212603414683</v>
       </c>
       <c r="D2" t="n">
-        <v>34.76564970278805</v>
+        <v>31.41199954508095</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98070920328033</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C3" t="n">
-        <v>25.02965771977243</v>
+        <v>20.75905520629881</v>
       </c>
       <c r="D3" t="n">
-        <v>39.24536447726624</v>
+        <v>45.56291095409447</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.0569667290421</v>
+        <v>30.52842661125882</v>
       </c>
       <c r="C4" t="n">
-        <v>59.9592592891697</v>
+        <v>47.10720009287471</v>
       </c>
       <c r="D4" t="n">
-        <v>30.83473189498382</v>
+        <v>37.01188845010475</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.05911015089984</v>
+        <v>40.96342295969817</v>
       </c>
       <c r="C5" t="n">
-        <v>52.96528864411543</v>
+        <v>78.61344741756335</v>
       </c>
       <c r="D5" t="n">
-        <v>27.36621725587985</v>
+        <v>32.66765485881262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.16858286768997</v>
+        <v>28.33716573537994</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5510068084565</v>
+        <v>80.5838150599867</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>17.48689010804419</v>
+        <v>39.76470901281281</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066511368326235</v>
+        <v>17.34672380662597</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24854407805844</v>
+        <v>115.3557133140627</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299883526244676</v>
+        <v>4.336680951656492</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.453608497091031</v>
+        <v>2.239366513386974</v>
       </c>
       <c r="C2" t="n">
-        <v>5.537057051952011</v>
+        <v>5.574363464713389</v>
       </c>
       <c r="D2" t="n">
-        <v>28.67488694564084</v>
+        <v>25.53525778745954</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.99820073550753</v>
+        <v>9.53277020823653</v>
       </c>
       <c r="C3" t="n">
-        <v>34.03719290623692</v>
+        <v>24.97075285751762</v>
       </c>
       <c r="D3" t="n">
-        <v>59.97987599095887</v>
+        <v>58.48271074198249</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.40454647407447</v>
+        <v>26.26567807941916</v>
       </c>
       <c r="C4" t="n">
-        <v>61.84814187214056</v>
+        <v>49.60869324329558</v>
       </c>
       <c r="D4" t="n">
-        <v>44.92477494633405</v>
+        <v>49.95328668748621</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.16482010778901</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>88.94634200476104</v>
+        <v>82.83496254582464</v>
       </c>
       <c r="D5" t="n">
-        <v>32.96217917008666</v>
+        <v>37.62548076525901</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.76105975943631</v>
+        <v>41.41895389446869</v>
       </c>
       <c r="C6" t="n">
-        <v>62.59132488425541</v>
+        <v>101.6756827380252</v>
       </c>
       <c r="D6" t="n">
-        <v>32.56358960216246</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>33.35684174719388</v>
+        <v>77.43338667705868</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>21.78007281871549</v>
+        <v>38.80357801035517</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290229837014074</v>
+        <v>17.74606591141775</v>
       </c>
       <c r="C21" t="n">
-        <v>75.63613455902102</v>
+        <v>128.6589778577787</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378951107387315</v>
+        <v>5.323819773425325</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.987278337573796</v>
+        <v>2.099958339383927</v>
       </c>
       <c r="C2" t="n">
-        <v>8.921141388490765</v>
+        <v>3.433171721751096</v>
       </c>
       <c r="D2" t="n">
-        <v>27.07071119690155</v>
+        <v>20.03943413908589</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3747909433108</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>26.46300936797277</v>
+        <v>35.50981446260713</v>
       </c>
       <c r="D3" t="n">
-        <v>69.00213739298707</v>
+        <v>63.43071917138642</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.05468443846411</v>
+        <v>20.80323385298991</v>
       </c>
       <c r="C4" t="n">
-        <v>75.64464235992098</v>
+        <v>72.30080967925635</v>
       </c>
       <c r="D4" t="n">
-        <v>64.87290654892499</v>
+        <v>47.00509833163304</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.5096755938869</v>
+        <v>23.31650797586175</v>
       </c>
       <c r="C5" t="n">
-        <v>102.641722479004</v>
+        <v>60.74563920027141</v>
       </c>
       <c r="D5" t="n">
-        <v>41.38066573400307</v>
+        <v>33.94392687433348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>106.6266364105418</v>
+        <v>50.99884799250906</v>
       </c>
       <c r="D6" t="n">
-        <v>36.02523200733671</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>64.91708519561608</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>34.29735604786232</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500739285499245</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32090937255391</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500739285499245</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
